--- a/public_reports/reports/history/build-local/Execution_Summary.xlsx
+++ b/public_reports/reports/history/build-local/Execution_Summary.xlsx
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>497</v>
+        <v>510</v>
       </c>
     </row>
     <row r="3">
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>97.45%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
